--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0002_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0002_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -9985,7 +9984,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L28" s="0">
         <v>0</v>
@@ -11421,7 +11420,7 @@
         <v>7.437376258930871</v>
       </c>
       <c r="G32" s="0">
-        <v>2.644230769230767</v>
+        <v>2.6442307692307669</v>
       </c>
       <c r="H32" s="0">
         <v>0.030275507114744145</v>
@@ -11783,7 +11782,7 @@
         <v>12.326762503228018</v>
       </c>
       <c r="G33" s="0">
-        <v>8.1330128205128141</v>
+        <v>8.133012820512814</v>
       </c>
       <c r="H33" s="0">
         <v>0.06055101422948829</v>
@@ -12857,7 +12856,7 @@
         <v>5.3687907676868996</v>
       </c>
       <c r="C36" s="0">
-        <v>5.3999116217410475</v>
+        <v>5.3999116217410474</v>
       </c>
       <c r="D36" s="0">
         <v>2.0572084255388883</v>
@@ -13016,7 +13015,7 @@
         <v>0.46978161503301125</v>
       </c>
       <c r="BD36" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE36" s="0">
         <v>0</v>
@@ -13240,7 +13239,7 @@
         <v>14.468438538205968</v>
       </c>
       <c r="J37" s="0">
-        <v>1.5921734126222889</v>
+        <v>1.5921734126222888</v>
       </c>
       <c r="K37" s="0">
         <v>0.11402508551881405</v>
@@ -13255,7 +13254,7 @@
         <v>15.887850467289704</v>
       </c>
       <c r="O37" s="0">
-        <v>1.0282776349614387</v>
+        <v>1.0282776349614386</v>
       </c>
       <c r="P37" s="0">
         <v>12.540522095205587</v>
@@ -13357,7 +13356,7 @@
         <v>0</v>
       </c>
       <c r="AW37" s="0">
-        <v>0.18837459634015053</v>
+        <v>0.18837459634015052</v>
       </c>
       <c r="AX37" s="0">
         <v>0</v>
@@ -13740,7 +13739,7 @@
         <v>6.6404266124936466</v>
       </c>
       <c r="BD38" s="0">
-        <v>0.76053442959917717</v>
+        <v>0.76053442959917716</v>
       </c>
       <c r="BE38" s="0">
         <v>0.18752930145335192</v>
@@ -14063,7 +14062,7 @@
         <v>0.61810154525386263</v>
       </c>
       <c r="AQ39" s="0">
-        <v>1.4163090128755354</v>
+        <v>1.4163090128755353</v>
       </c>
       <c r="AR39" s="0">
         <v>0</v>
@@ -14213,7 +14212,7 @@
         <v>0</v>
       </c>
       <c r="CO39" s="0">
-        <v>2.6976990214229018</v>
+        <v>2.6976990214229017</v>
       </c>
       <c r="CP39" s="0">
         <v>0</v>
@@ -14299,7 +14298,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>5.3254437869822438</v>
+        <v>5.3254437869822437</v>
       </c>
       <c r="B40" s="0">
         <v>0</v>
@@ -14563,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="CK40" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL40" s="0">
         <v>0.085259568018188639</v>
@@ -14590,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="CT40" s="0">
-        <v>4.7657188626351577</v>
+        <v>4.7657188626351576</v>
       </c>
       <c r="CU40" s="0">
         <v>0</v>
@@ -14784,7 +14783,7 @@
         <v>5.21348314606744</v>
       </c>
       <c r="AP41" s="0">
-        <v>6.6666666666666981</v>
+        <v>6.666666666666698</v>
       </c>
       <c r="AQ41" s="0">
         <v>9.3133047210300859</v>
@@ -15134,7 +15133,7 @@
         <v>12.502785825718732</v>
       </c>
       <c r="AL42" s="0">
-        <v>0.5416908492938668</v>
+        <v>0.54169084929386679</v>
       </c>
       <c r="AM42" s="0">
         <v>0.55607043558850744</v>
@@ -15146,7 +15145,7 @@
         <v>11.01123595505617</v>
       </c>
       <c r="AP42" s="0">
-        <v>9.8896247240618021</v>
+        <v>9.889624724061802</v>
       </c>
       <c r="AQ42" s="0">
         <v>13.776824034334751</v>
@@ -15427,7 +15426,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="0">
-        <v>5.5566541427723895</v>
+        <v>5.5566541427723894</v>
       </c>
       <c r="P43" s="0">
         <v>0.05118580447022688</v>
@@ -15529,7 +15528,7 @@
         <v>0.11178180192264689</v>
       </c>
       <c r="AW43" s="0">
-        <v>7.9655543595263652</v>
+        <v>7.9655543595263651</v>
       </c>
       <c r="AX43" s="0">
         <v>0</v>
@@ -15619,7 +15618,7 @@
         <v>10.031595576619264</v>
       </c>
       <c r="CA43" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="CB43" s="0">
         <v>3.4645669291338552</v>
@@ -15646,7 +15645,7 @@
         <v>0.033277870216306127</v>
       </c>
       <c r="CJ43" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK43" s="0">
         <v>3.7718177948062976</v>
@@ -15667,7 +15666,7 @@
         <v>0.67154335052164471</v>
       </c>
       <c r="CQ43" s="0">
-        <v>0.68270481144343243</v>
+        <v>0.68270481144343242</v>
       </c>
       <c r="CR43" s="0">
         <v>0.031959092361776895</v>
@@ -15685,7 +15684,7 @@
         <v>0</v>
       </c>
       <c r="CW43" s="0">
-        <v>1.9293775027302496</v>
+        <v>1.9293775027302495</v>
       </c>
       <c r="CX43" s="0">
         <v>0</v>
@@ -15736,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="DN43" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO43" s="0">
         <v>0</v>
@@ -15921,7 +15920,7 @@
         <v>4.7896709704289835</v>
       </c>
       <c r="BG44" s="0">
-        <v>2.4953789279112733</v>
+        <v>2.4953789279112732</v>
       </c>
       <c r="BH44" s="0">
         <v>0.033467202141900909</v>
@@ -15969,7 +15968,7 @@
         <v>0.63882063882063833</v>
       </c>
       <c r="BW44" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX44" s="0">
         <v>0.084139671855279694</v>
@@ -16035,10 +16034,10 @@
         <v>0.063918184723553789</v>
       </c>
       <c r="CS44" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT44" s="0">
-        <v>8.5302362835402406</v>
+        <v>8.5302362835402405</v>
       </c>
       <c r="CU44" s="0">
         <v>0</v>
@@ -16092,7 +16091,7 @@
         <v>2.011095700416087</v>
       </c>
       <c r="DL44" s="0">
-        <v>8.8772845953002531</v>
+        <v>8.877284595300253</v>
       </c>
       <c r="DM44" s="0">
         <v>0</v>
@@ -16196,13 +16195,13 @@
         <v>8.581560283687935</v>
       </c>
       <c r="AD45" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE45" s="0">
         <v>0</v>
       </c>
       <c r="AF45" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="AG45" s="0">
         <v>0.022634676324128546</v>
@@ -16295,7 +16294,7 @@
         <v>2.3770038695411806</v>
       </c>
       <c r="BK45" s="0">
-        <v>4.5126725736657694</v>
+        <v>4.5126725736657693</v>
       </c>
       <c r="BL45" s="0">
         <v>12.705387848681685</v>
@@ -16439,7 +16438,7 @@
         <v>0.051124744376278078</v>
       </c>
       <c r="DG45" s="0">
-        <v>14.024390243902428</v>
+        <v>14.024390243902427</v>
       </c>
       <c r="DH45" s="0">
         <v>0.53475935828876953</v>
@@ -16624,7 +16623,7 @@
         <v>14.317492416582393</v>
       </c>
       <c r="AZ46" s="0">
-        <v>3.4827713968136314</v>
+        <v>3.4827713968136313</v>
       </c>
       <c r="BA46" s="0">
         <v>14.564328405158841</v>
@@ -16959,7 +16958,7 @@
         <v>0.26490066225165687</v>
       </c>
       <c r="AQ47" s="0">
-        <v>0.17167381974249008</v>
+        <v>0.17167381974249007</v>
       </c>
       <c r="AR47" s="0">
         <v>6.9532710280374159</v>
@@ -17019,7 +17018,7 @@
         <v>0.099502487562189518</v>
       </c>
       <c r="BK47" s="0">
-        <v>0.22666391922522256</v>
+        <v>0.22666391922522255</v>
       </c>
       <c r="BL47" s="0">
         <v>6.1902942300344197</v>
@@ -17058,7 +17057,7 @@
         <v>7.5000000000000346</v>
       </c>
       <c r="BX47" s="0">
-        <v>4.7959612957509688</v>
+        <v>4.7959612957509687</v>
       </c>
       <c r="BY47" s="0">
         <v>7.6086956521739486</v>
@@ -17270,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="0">
-        <v>5.0102951269732286</v>
+        <v>5.0102951269732285</v>
       </c>
       <c r="AA48" s="0">
         <v>14.775725593667532</v>
@@ -17644,7 +17643,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="0">
-        <v>9.0649536045681583</v>
+        <v>9.0649536045681582</v>
       </c>
       <c r="AE49" s="0">
         <v>0.6147540983606552</v>
@@ -17869,7 +17868,7 @@
         <v>0.023304591004427853</v>
       </c>
       <c r="DA49" s="0">
-        <v>2.7377521613832832</v>
+        <v>2.7377521613832831</v>
       </c>
       <c r="DB49" s="0">
         <v>0.15673981191222555</v>
@@ -17914,7 +17913,7 @@
         <v>15.048543689320374</v>
       </c>
       <c r="DP49" s="0">
-        <v>19.718309859154911</v>
+        <v>19.71830985915491</v>
       </c>
     </row>
     <row r="50">
@@ -18129,7 +18128,7 @@
         <v>0.096875756841850236</v>
       </c>
       <c r="BS50" s="0">
-        <v>8.4696474009451031</v>
+        <v>8.469647400945103</v>
       </c>
       <c r="BT50" s="0">
         <v>12.515899262274219</v>
@@ -18219,7 +18218,7 @@
         <v>17.164179104477597</v>
       </c>
       <c r="CW50" s="0">
-        <v>1.2377138696760091</v>
+        <v>1.237713869676009</v>
       </c>
       <c r="CX50" s="0">
         <v>11.888782358581006</v>
@@ -18243,7 +18242,7 @@
         <v>4.4990892531876101</v>
       </c>
       <c r="DE50" s="0">
-        <v>0.19333011116481375</v>
+        <v>0.19333011116481374</v>
       </c>
       <c r="DF50" s="0">
         <v>13.548057259713691</v>
@@ -18258,7 +18257,7 @@
         <v>0</v>
       </c>
       <c r="DJ50" s="0">
-        <v>9.9593495934959258</v>
+        <v>9.9593495934959257</v>
       </c>
       <c r="DK50" s="0">
         <v>1.733703190013868</v>
@@ -18374,7 +18373,7 @@
         <v>3.6885245901639312</v>
       </c>
       <c r="AF51" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="AG51" s="0">
         <v>12.177455862381157</v>
@@ -18482,7 +18481,7 @@
         <v>0</v>
       </c>
       <c r="BP51" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ51" s="0">
         <v>0</v>
@@ -18506,7 +18505,7 @@
         <v>6.6228070175438534</v>
       </c>
       <c r="BX51" s="0">
-        <v>8.2877576777450504</v>
+        <v>8.2877576777450503</v>
       </c>
       <c r="BY51" s="0">
         <v>0</v>
@@ -18560,7 +18559,7 @@
         <v>0</v>
       </c>
       <c r="CP51" s="0">
-        <v>0.43170643962105732</v>
+        <v>0.43170643962105731</v>
       </c>
       <c r="CQ51" s="0">
         <v>0.29258777633289962</v>
@@ -18635,7 +18634,7 @@
         <v>0.39062499999999967</v>
       </c>
       <c r="DO51" s="0">
-        <v>2.9126213592232984</v>
+        <v>2.9126213592232983</v>
       </c>
       <c r="DP51" s="0">
         <v>6.3380281690140787</v>
@@ -18772,7 +18771,7 @@
         <v>0</v>
       </c>
       <c r="AR52" s="0">
-        <v>1.3084112149532699</v>
+        <v>1.3084112149532698</v>
       </c>
       <c r="AS52" s="0">
         <v>0.19841269841269824</v>
@@ -18931,7 +18930,7 @@
         <v>1.9015659955257254</v>
       </c>
       <c r="CS52" s="0">
-        <v>2.1892967713401133</v>
+        <v>2.1892967713401132</v>
       </c>
       <c r="CT52" s="0">
         <v>0</v>
@@ -19439,7 +19438,7 @@
         <v>0</v>
       </c>
       <c r="Y54" s="0">
-        <v>14.779874213836465</v>
+        <v>14.779874213836464</v>
       </c>
       <c r="Z54" s="0">
         <v>0</v>
@@ -19484,7 +19483,7 @@
         <v>0</v>
       </c>
       <c r="AN54" s="0">
-        <v>4.4328552803129036</v>
+        <v>4.4328552803129035</v>
       </c>
       <c r="AO54" s="0">
         <v>0</v>
@@ -19496,7 +19495,7 @@
         <v>0</v>
       </c>
       <c r="AR54" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS54" s="0">
         <v>0</v>
@@ -19795,7 +19794,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="0">
-        <v>0.66666666666666608</v>
+        <v>0.66666666666666607</v>
       </c>
       <c r="X55" s="0">
         <v>0</v>
@@ -19816,7 +19815,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE55" s="0">
         <v>10.245901639344254</v>
@@ -20178,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="AD56" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE56" s="0">
         <v>4.5081967213114718</v>
@@ -20543,7 +20542,7 @@
         <v>0</v>
       </c>
       <c r="AE57" s="0">
-        <v>1.229508196721324</v>
+        <v>1.2295081967213239</v>
       </c>
       <c r="AF57" s="0">
         <v>0</v>
@@ -20591,7 +20590,7 @@
         <v>5.0083472454090661</v>
       </c>
       <c r="AU57" s="0">
-        <v>0.018545994065282089</v>
+        <v>0.018545994065282088</v>
       </c>
       <c r="AV57" s="0">
         <v>0</v>
@@ -24938,7 +24937,7 @@
         <v>12.295994065282025</v>
       </c>
       <c r="AV69" s="0">
-        <v>0.20120724346076666</v>
+        <v>0.20120724346076665</v>
       </c>
       <c r="AW69" s="0">
         <v>0</v>
@@ -25483,7 +25482,7 @@
         <v>0</v>
       </c>
       <c r="DE70" s="0">
-        <v>0.096665055582406873</v>
+        <v>0.096665055582406872</v>
       </c>
       <c r="DF70" s="0">
         <v>7.6687116564417108</v>
@@ -25611,7 +25610,7 @@
         <v>1.4275517487508909</v>
       </c>
       <c r="AE71" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF71" s="0">
         <v>0</v>
@@ -25650,7 +25649,7 @@
         <v>0</v>
       </c>
       <c r="AR71" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS71" s="0">
         <v>0</v>
@@ -25674,7 +25673,7 @@
         <v>0</v>
       </c>
       <c r="AZ71" s="0">
-        <v>3.1307891811782112</v>
+        <v>3.1307891811782111</v>
       </c>
       <c r="BA71" s="0">
         <v>0</v>
@@ -25955,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="Y72" s="0">
-        <v>8.8050314465408715</v>
+        <v>8.8050314465408714</v>
       </c>
       <c r="Z72" s="0">
         <v>0</v>
@@ -25994,7 +25993,7 @@
         <v>0</v>
       </c>
       <c r="AL72" s="0">
-        <v>0.5416908492938668</v>
+        <v>0.54169084929386679</v>
       </c>
       <c r="AM72" s="0">
         <v>0</v>
@@ -26401,10 +26400,10 @@
         <v>12.282326787699137</v>
       </c>
       <c r="BA73" s="0">
-        <v>0.22019502988361101</v>
+        <v>0.220195029883611</v>
       </c>
       <c r="BB73" s="0">
-        <v>3.8734476641040772</v>
+        <v>3.8734476641040771</v>
       </c>
       <c r="BC73" s="0">
         <v>0</v>
@@ -26506,7 +26505,7 @@
         <v>0</v>
       </c>
       <c r="CJ73" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK73" s="0">
         <v>0</v>
@@ -26527,7 +26526,7 @@
         <v>0</v>
       </c>
       <c r="CQ73" s="0">
-        <v>4.0799739921976555</v>
+        <v>4.0799739921976554</v>
       </c>
       <c r="CR73" s="0">
         <v>11.920741450942781</v>
@@ -26826,7 +26825,7 @@
         <v>0</v>
       </c>
       <c r="BV74" s="0">
-        <v>1.3267813267813256</v>
+        <v>1.3267813267813255</v>
       </c>
       <c r="BW74" s="0">
         <v>0</v>
@@ -26889,7 +26888,7 @@
         <v>0</v>
       </c>
       <c r="CQ74" s="0">
-        <v>8.289986996098822</v>
+        <v>8.2899869960988219</v>
       </c>
       <c r="CR74" s="0">
         <v>7.750079897730898</v>
@@ -27194,7 +27193,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="BX75" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY75" s="0">
         <v>0.041806020066889597</v>
@@ -27233,13 +27232,13 @@
         <v>1.5812776723592648</v>
       </c>
       <c r="CK75" s="0">
-        <v>0.17879948914431657</v>
+        <v>0.17879948914431656</v>
       </c>
       <c r="CL75" s="0">
         <v>0</v>
       </c>
       <c r="CM75" s="0">
-        <v>7.4343208496366629</v>
+        <v>7.4343208496366628</v>
       </c>
       <c r="CN75" s="0">
         <v>11.162957645369696</v>
@@ -27254,7 +27253,7 @@
         <v>12.548764629388806</v>
       </c>
       <c r="CR75" s="0">
-        <v>3.1000319590923589</v>
+        <v>3.1000319590923588</v>
       </c>
       <c r="CS75" s="0">
         <v>10.017691287041123</v>
@@ -27397,7 +27396,7 @@
         <v>0</v>
       </c>
       <c r="W76" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X76" s="0">
         <v>8.8118249005116471</v>
@@ -27595,7 +27594,7 @@
         <v>4.1429475015812738</v>
       </c>
       <c r="CK76" s="0">
-        <v>1.0727969348658995</v>
+        <v>1.0727969348658994</v>
       </c>
       <c r="CL76" s="0">
         <v>0</v>
@@ -27855,13 +27854,13 @@
         <v>7.3920756948551096</v>
       </c>
       <c r="BC77" s="0">
-        <v>0.050787201625190404</v>
+        <v>0.050787201625190403</v>
       </c>
       <c r="BD77" s="0">
         <v>0.28776978417266164</v>
       </c>
       <c r="BE77" s="0">
-        <v>2.625410220346927</v>
+        <v>2.6254102203469269</v>
       </c>
       <c r="BF77" s="0">
         <v>4.5814244064972884</v>
@@ -28017,7 +28016,7 @@
         <v>10.965391621129317</v>
       </c>
       <c r="DE77" s="0">
-        <v>8.8931851135814331</v>
+        <v>8.893185113581433</v>
       </c>
       <c r="DF77" s="0">
         <v>0</v>
@@ -28166,7 +28165,7 @@
         <v>3.0755515934923086</v>
       </c>
       <c r="AL78" s="0">
-        <v>3.9272586573805342</v>
+        <v>3.9272586573805341</v>
       </c>
       <c r="AM78" s="0">
         <v>11.02873030583873</v>
@@ -28265,7 +28264,7 @@
         <v>8.912569629450223</v>
       </c>
       <c r="BS78" s="0">
-        <v>0.27868653822852269</v>
+        <v>0.27868653822852268</v>
       </c>
       <c r="BT78" s="0">
         <v>0</v>
@@ -28307,7 +28306,7 @@
         <v>0</v>
       </c>
       <c r="CG78" s="0">
-        <v>3.2263783017195507</v>
+        <v>3.2263783017195506</v>
       </c>
       <c r="CH78" s="0">
         <v>0.026500596263415901</v>
@@ -28331,7 +28330,7 @@
         <v>2.045944005742999</v>
       </c>
       <c r="CO78" s="0">
-        <v>7.8682888124834634</v>
+        <v>7.8682888124834633</v>
       </c>
       <c r="CP78" s="0">
         <v>0.02398369109005874</v>
@@ -28364,7 +28363,7 @@
         <v>10.989545344031111</v>
       </c>
       <c r="CZ78" s="0">
-        <v>7.7371242134700467</v>
+        <v>7.7371242134700466</v>
       </c>
       <c r="DA78" s="0">
         <v>0</v>
@@ -28501,10 +28500,10 @@
         <v>6.9282648681790242</v>
       </c>
       <c r="AC79" s="0">
-        <v>3.6170212765957413</v>
+        <v>3.6170212765957412</v>
       </c>
       <c r="AD79" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE79" s="0">
         <v>1.0245901639344253</v>
@@ -28657,7 +28656,7 @@
         <v>11.181102362204715</v>
       </c>
       <c r="CC79" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD79" s="0">
         <v>1.2307692307692297</v>
@@ -28866,10 +28865,10 @@
         <v>9.0780141843971549</v>
       </c>
       <c r="AD80" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE80" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF80" s="0">
         <v>0.84210526315789402</v>
@@ -29040,7 +29039,7 @@
         <v>9.9168053244592258</v>
       </c>
       <c r="CJ80" s="0">
-        <v>4.2061986084756447</v>
+        <v>4.2061986084756446</v>
       </c>
       <c r="CK80" s="0">
         <v>11.03448275862068</v>
@@ -29103,7 +29102,7 @@
         <v>1.8579234972677579</v>
       </c>
       <c r="DE80" s="0">
-        <v>0.096665055582406873</v>
+        <v>0.096665055582406872</v>
       </c>
       <c r="DF80" s="0">
         <v>0</v>
@@ -29240,7 +29239,7 @@
         <v>0.045269352648257093</v>
       </c>
       <c r="AH81" s="0">
-        <v>9.4196003805899054</v>
+        <v>9.4196003805899053</v>
       </c>
       <c r="AI81" s="0">
         <v>0</v>
@@ -29423,7 +29422,7 @@
         <v>2.9020266218971074</v>
       </c>
       <c r="CQ81" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR81" s="0">
         <v>0</v>
@@ -29566,7 +29565,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="0">
-        <v>1.8382352941176659</v>
+        <v>1.8382352941176658</v>
       </c>
       <c r="W82" s="0">
         <v>0</v>
@@ -29596,7 +29595,7 @@
         <v>0</v>
       </c>
       <c r="AF82" s="0">
-        <v>7.1578947368421782</v>
+        <v>7.1578947368421781</v>
       </c>
       <c r="AG82" s="0">
         <v>0</v>
@@ -29653,7 +29652,7 @@
         <v>0</v>
       </c>
       <c r="AY82" s="0">
-        <v>1.152679474216392</v>
+        <v>1.1526794742163919</v>
       </c>
       <c r="AZ82" s="0">
         <v>0</v>
@@ -29698,7 +29697,7 @@
         <v>0.59099600208587433</v>
       </c>
       <c r="BN82" s="0">
-        <v>2.5147469729897805</v>
+        <v>2.5147469729897804</v>
       </c>
       <c r="BO82" s="0">
         <v>0.54035798716650341</v>
@@ -29973,7 +29972,7 @@
         <v>0.52631578947368374</v>
       </c>
       <c r="AK83" s="0">
-        <v>3.1646980164920851</v>
+        <v>3.164698016492085</v>
       </c>
       <c r="AL83" s="0">
         <v>0</v>
@@ -30126,7 +30125,7 @@
         <v>0.66555740432612254</v>
       </c>
       <c r="CJ83" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK83" s="0">
         <v>0.68965517241379248</v>
@@ -30682,7 +30681,7 @@
         <v>0</v>
       </c>
       <c r="AF85" s="0">
-        <v>4.4210526315789434</v>
+        <v>4.4210526315789433</v>
       </c>
       <c r="AG85" s="0">
         <v>0</v>
@@ -30838,7 +30837,7 @@
         <v>8.3809523809523725</v>
       </c>
       <c r="CF85" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG85" s="0">
         <v>0</v>
@@ -30856,7 +30855,7 @@
         <v>0.0085142613878245992</v>
       </c>
       <c r="CL85" s="0">
-        <v>2.2925350511557388</v>
+        <v>2.2925350511557387</v>
       </c>
       <c r="CM85" s="0">
         <v>0</v>
@@ -30880,7 +30879,7 @@
         <v>0</v>
       </c>
       <c r="CT85" s="0">
-        <v>1.7220664797757293</v>
+        <v>1.7220664797757292</v>
       </c>
       <c r="CU85" s="0">
         <v>5.9880239520958032</v>
@@ -30966,7 +30965,7 @@
         <v>0.88776749836463809</v>
       </c>
       <c r="F86" s="0">
-        <v>0.73168632176981952</v>
+        <v>0.73168632176981951</v>
       </c>
       <c r="G86" s="0">
         <v>0</v>
@@ -31044,7 +31043,7 @@
         <v>0</v>
       </c>
       <c r="AF86" s="0">
-        <v>1.6842105263157881</v>
+        <v>1.684210526315788</v>
       </c>
       <c r="AG86" s="0">
         <v>0</v>
@@ -31134,7 +31133,7 @@
         <v>0</v>
       </c>
       <c r="BJ86" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK86" s="0">
         <v>0</v>
@@ -31343,7 +31342,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="0">
-        <v>6.7274800456100286</v>
+        <v>6.7274800456100285</v>
       </c>
       <c r="L87" s="0">
         <v>0.79914757591901897</v>
@@ -31607,7 +31606,7 @@
         <v>0.10012014417300752</v>
       </c>
       <c r="CU87" s="0">
-        <v>4.491017964071852</v>
+        <v>4.4910179640718519</v>
       </c>
       <c r="CV87" s="0">
         <v>1.3059701492537301</v>
@@ -31732,7 +31731,7 @@
         <v>0</v>
       </c>
       <c r="T88" s="0">
-        <v>1.4955951649252191</v>
+        <v>1.495595164925219</v>
       </c>
       <c r="U88" s="0">
         <v>0</v>
@@ -33503,7 +33502,7 @@
         <v>1.2395627098218118</v>
       </c>
       <c r="G93" s="0">
-        <v>3.8461538461538432</v>
+        <v>3.8461538461538431</v>
       </c>
       <c r="H93" s="0">
         <v>6.6303360581289672</v>
@@ -33883,7 +33882,7 @@
         <v>1.1188066062866391</v>
       </c>
       <c r="M94" s="0">
-        <v>0.33264033264033605</v>
+        <v>0.33264033264033604</v>
       </c>
       <c r="N94" s="0">
         <v>8.2866043613708023</v>
@@ -35337,7 +35336,7 @@
         <v>0.031152647975077854</v>
       </c>
       <c r="O98" s="0">
-        <v>5.6753015621910175</v>
+        <v>5.6753015621910174</v>
       </c>
       <c r="P98" s="0">
         <v>0.25592902235113441</v>
@@ -35711,7 +35710,7 @@
         <v>0.41322314049586739</v>
       </c>
       <c r="S99" s="0">
-        <v>2.2847589857899116</v>
+        <v>2.2847589857899115</v>
       </c>
       <c r="T99" s="0">
         <v>0</v>
